--- a/en/downloads/data-excel/7.1.2.xlsx
+++ b/en/downloads/data-excel/7.1.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -402,10 +402,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="###0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -546,6 +547,27 @@
     </font>
     <font>
       <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -616,7 +638,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -732,6 +754,15 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1038,13 +1069,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -1055,7 +1086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="43" t="s">
         <v>94</v>
       </c>
@@ -1068,14 +1099,15 @@
       <c r="D2" s="23"/>
       <c r="E2" s="23"/>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23"/>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
       <c r="D3" s="23"/>
       <c r="E3" s="23"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="47"/>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
@@ -1103,8 +1135,11 @@
       <c r="I4" s="26">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="26">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>24</v>
       </c>
@@ -1132,8 +1167,11 @@
       <c r="I5" s="33">
         <v>19.934537450516849</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="48">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>52</v>
       </c>
@@ -1149,8 +1187,9 @@
       <c r="G6" s="34"/>
       <c r="H6" s="34"/>
       <c r="I6" s="34"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="49"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="27" t="s">
         <v>53</v>
       </c>
@@ -1178,8 +1217,11 @@
       <c r="I7" s="34">
         <v>50.663874100635795</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="50">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
         <v>54</v>
       </c>
@@ -1207,8 +1249,11 @@
       <c r="I8" s="34">
         <v>2.3700432917533609</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="50">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
         <v>85</v>
       </c>
@@ -1224,8 +1269,9 @@
       <c r="G9" s="38"/>
       <c r="H9" s="38"/>
       <c r="I9" s="38"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="49"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="40" t="s">
         <v>88</v>
       </c>
@@ -1253,8 +1299,11 @@
       <c r="I10" s="41">
         <v>18.286297303548345</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="50">
+        <v>53.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="40" t="s">
         <v>91</v>
       </c>
@@ -1282,8 +1331,11 @@
       <c r="I11" s="41">
         <v>21.435728095612447</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="50">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
@@ -1296,8 +1348,9 @@
       <c r="D12" s="9"/>
       <c r="E12" s="29"/>
       <c r="F12" s="29"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="49"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>56</v>
       </c>
@@ -1325,8 +1378,11 @@
       <c r="I13" s="34">
         <v>5.3208076880709658</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="50">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>57</v>
       </c>
@@ -1354,8 +1410,11 @@
       <c r="I14" s="34">
         <v>16.243664579284424</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="50">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>58</v>
       </c>
@@ -1383,8 +1442,11 @@
       <c r="I15" s="34">
         <v>7.6579228718220209</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="50">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>59</v>
       </c>
@@ -1412,8 +1474,11 @@
       <c r="I16" s="34">
         <v>10.866087439303547</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="50">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>60</v>
       </c>
@@ -1441,8 +1506,11 @@
       <c r="I17" s="34">
         <v>0.79569676176021309</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="50">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>61</v>
       </c>
@@ -1470,8 +1538,11 @@
       <c r="I18" s="34">
         <v>8.2997858070723236</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="50">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>62</v>
       </c>
@@ -1499,8 +1570,11 @@
       <c r="I19" s="34">
         <v>15.806671262907001</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="50">
+        <v>18.100000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>63</v>
       </c>
@@ -1528,8 +1602,11 @@
       <c r="I20" s="34">
         <v>68.945554947895289</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="50">
+        <v>73.400000000000006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>64</v>
       </c>
@@ -1557,8 +1634,11 @@
       <c r="I21" s="34">
         <v>30.425502249062689</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J21" s="50">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>76</v>
       </c>
@@ -1571,8 +1651,9 @@
       <c r="D22" s="9"/>
       <c r="E22" s="29"/>
       <c r="F22" s="29"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="49"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="27" t="s">
         <v>65</v>
       </c>
@@ -1600,8 +1681,11 @@
       <c r="I23" s="30">
         <v>14.976208293126314</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="50">
+        <v>21.581441625240842</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="27" t="s">
         <v>66</v>
       </c>
@@ -1629,8 +1713,11 @@
       <c r="I24" s="30">
         <v>17.392665205439346</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="50">
+        <v>18.23722841223239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="27" t="s">
         <v>67</v>
       </c>
@@ -1658,8 +1745,11 @@
       <c r="I25" s="30">
         <v>20.618935335405116</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="50">
+        <v>18.378469760338866</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
         <v>68</v>
       </c>
@@ -1687,8 +1777,11 @@
       <c r="I26" s="30">
         <v>22.148258554308065</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="50">
+        <v>30.703219597568648</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="27" t="s">
         <v>69</v>
       </c>
@@ -1716,8 +1809,11 @@
       <c r="I27" s="30">
         <v>21.800264520143493</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J27" s="50">
+        <v>47.583105652978688</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>75</v>
       </c>
@@ -1733,8 +1829,9 @@
       <c r="G28" s="31"/>
       <c r="H28" s="31"/>
       <c r="I28" s="31"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="49"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>70</v>
       </c>
@@ -1762,8 +1859,11 @@
       <c r="I29" s="30">
         <v>15.062506611764045</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="50">
+        <v>19.834842287086513</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>71</v>
       </c>
@@ -1791,8 +1891,11 @@
       <c r="I30" s="30">
         <v>17.066945082408946</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="50">
+        <v>20.985180369341972</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>72</v>
       </c>
@@ -1820,8 +1923,11 @@
       <c r="I31" s="30">
         <v>17.11785730812262</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="50">
+        <v>24.401929393805439</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>73</v>
       </c>
@@ -1849,8 +1955,11 @@
       <c r="I32" s="30">
         <v>22.725888265024722</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J32" s="50">
+        <v>25.420980467399804</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>74</v>
       </c>
@@ -1878,8 +1987,11 @@
       <c r="I33" s="32">
         <v>27.767655316422797</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="J33" s="51">
+        <v>32.879737660073275</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A34" s="45" t="s">
         <v>101</v>
       </c>
@@ -1892,7 +2004,7 @@
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
     </row>
-    <row r="35" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="46" t="s">
         <v>97</v>
       </c>
@@ -1905,7 +2017,7 @@
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="23"/>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
